--- a/weather_data.xlsx
+++ b/weather_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6922,6 +6922,70 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>288.69</v>
+      </c>
+      <c r="C204" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="D204" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2026-04-13u 18:03:52</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>69</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1021</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>288.69</v>
+      </c>
+      <c r="C205" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="D205" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-04-13u 18:03:58</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>69</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1021</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weather_data.xlsx
+++ b/weather_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6986,6 +6986,262 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>297.54</v>
+      </c>
+      <c r="C206" t="n">
+        <v>297.03</v>
+      </c>
+      <c r="D206" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2026-04-20u 18:54:36</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>38</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1009</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>clear sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>297.54</v>
+      </c>
+      <c r="C207" t="n">
+        <v>297.03</v>
+      </c>
+      <c r="D207" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>2026-04-20u 18:54:42</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>38</v>
+      </c>
+      <c r="G207" t="n">
+        <v>1009</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>clear sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>297.54</v>
+      </c>
+      <c r="C208" t="n">
+        <v>297.03</v>
+      </c>
+      <c r="D208" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>2026-04-20u 18:56:47</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>38</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1009</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>clear sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>297.54</v>
+      </c>
+      <c r="C209" t="n">
+        <v>297.03</v>
+      </c>
+      <c r="D209" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2026-04-20u 18:56:53</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>38</v>
+      </c>
+      <c r="G209" t="n">
+        <v>1009</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>clear sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>24</v>
+      </c>
+      <c r="C210" t="n">
+        <v>24</v>
+      </c>
+      <c r="D210" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2026-04-20 19:00:10</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>38</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1009</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>clear sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>24</v>
+      </c>
+      <c r="C211" t="n">
+        <v>24</v>
+      </c>
+      <c r="D211" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2026-04-20 19:00:16</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>38</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1009</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>clear sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>24</v>
+      </c>
+      <c r="C212" t="n">
+        <v>24</v>
+      </c>
+      <c r="D212" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>2026-04-20 19:02:21</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>38</v>
+      </c>
+      <c r="G212" t="n">
+        <v>1009</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>clear sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>24</v>
+      </c>
+      <c r="C213" t="n">
+        <v>24</v>
+      </c>
+      <c r="D213" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2026-04-20 19:02:26</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>38</v>
+      </c>
+      <c r="G213" t="n">
+        <v>1009</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>clear sky</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
